--- a/data/excel/applications.xlsx
+++ b/data/excel/applications.xlsx
@@ -593,32 +593,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIFbGnyL7dgiyPym8h0ZQ0JlhfVxDKjAAI9GGsbWXGRS0EwTVWBYPv4AQADAgADeAADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIFbGnyL7dgiyPym8h0ZQ0JlhfVxDKjAAI9GGsbWXGRS0EwTVWBYPv4AQADAgADeAADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIGd2n1-DmpnC5Fkqj2KtSRV6jRE11WAAKaFmsbQ0-wS3rh5GN7NzPMAQADAgADeAADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIFbGnyL7dgiyPym8h0ZQ0JlhfVxDKjAAI9GGsbWXGRS0EwTVWBYPv4AQADAgADeAADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIFbGnyL7dgiyPym8h0ZQ0JlhfVxDKjAAI9GGsbWXGRS0EwTVWBYPv4AQADAgADeAADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
+          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIFbGnyL7dgiyPym8h0ZQ0JlhfVxDKjAAI9GGsbWXGRS0EwTVWBYPv4AQADAgADeAADOwQ; server_path: data/files/5394280567/ent_certificate.jpg</t>
+          <t>Telegram file_id: BQACAgIAAxkBAAIGfmn1-GtuhrNEfSdXuzI1rQ4X_nZHAALhlgACQ0-wS-JqAuZDngukOwQ; server_path: data/files/5394280567/ent_certificate.zip</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>jhgk</t>
+          <t>efefef</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -633,11 +633,15 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>450000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1800000</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>pending</t>

--- a/data/excel/applications.xlsx
+++ b/data/excel/applications.xlsx
@@ -8,7 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applicants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Applicants'!$A$1:$V$2</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -54,9 +56,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -426,8 +429,28 @@
   <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="17" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,132 +466,132 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Telegram Profile</t>
+          <t>Ссылка Telegram</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Full Name</t>
+          <t>ФИО</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Телефон</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Faculty</t>
+          <t>Бірлестік / кафедра</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Specialty</t>
+          <t>Специальность</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Курс</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Группа</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Diploma File</t>
+          <t>Аттестат/диплом</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ID Card File</t>
+          <t>Удостоверение личности</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Photo 3x4 File</t>
+          <t>Фото 3x4</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Medical 075/у File</t>
+          <t>Справка 075/у</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ENT Certificate File</t>
+          <t>Сертификат ЕНТ</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Источник</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Admission Faculty</t>
+          <t>Бірлестік / кафедра (поступление)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Admission Specialty</t>
+          <t>Специальность поступления</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Calculated Discount</t>
+          <t>Расчетная скидка</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Calculated Year Price</t>
+          <t>Расчетная цена за год</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Calculated Total Price</t>
+          <t>Расчетная цена за 4 года</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Review Status</t>
+          <t>Статус проверки</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5394280567</v>
+        <v>7939104831</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>spisoq</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>https://t.me/spisoq</t>
+          <t>kotakbaser</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://t.me/kotakbaser</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rjrrk ej'</t>
+          <t>алалла</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+77700042874</t>
+          <t>+77382873728</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -593,65 +616,55 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/attestat_diplom.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGd2n1-DmpnC5Fkqj2KtSRV6jRE11WAAKaFmsbQ0-wS3rh5GN7NzPMAQADAgADeAADOwQ; server_path: data/files/5394280567/udostoverenie.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/photo_3x4.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Telegram file_id: AgACAgIAAxkBAAIGX2n19XYlXHX44iZe5GA6NSu_-8MwAAKTFmsbQ0-wS8UZSZRCqIUZAQADAgADeQADOwQ; server_path: data/files/5394280567/med_075u.jpg</t>
+          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Telegram file_id: BQACAgIAAxkBAAIGfmn1-GtuhrNEfSdXuzI1rQ4X_nZHAALhlgACQ0-wS-JqAuZDngukOwQ; server_path: data/files/5394280567/ent_certificate.zip</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>efefef</t>
-        </is>
-      </c>
+          <t>Telegram file_id: AgACAgQAAxkBAAIE7GnrUb_a-6Wp9etMHyL8ZQS54dk-AALwC2sbXwNZU5dexFTzM8eSAQADAgADeAADOwQ</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Инженерные технологии</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>6B11380 - Вычислительная техника и программное обеспечение</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>450000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1800000</v>
-      </c>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-  </hyperlinks>
+  <autoFilter ref="A1:V2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>